--- a/Correction CSGames.xlsx
+++ b/Correction CSGames.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>Page</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Points</t>
   </si>
   <si>
+    <t>Complété</t>
+  </si>
+  <si>
     <t>Barre de navigation</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
   <si>
     <t>Navigation Bar</t>
@@ -383,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -392,6 +398,9 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -409,8 +418,12 @@
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -420,9 +433,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -662,534 +672,669 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7">
-        <v>5.0</v>
+      <c r="A3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D3" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7">
-        <v>5.0</v>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D4" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="6"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7">
-        <v>2.0</v>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2.0</v>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D8" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.0</v>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D9" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2.0</v>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5.0</v>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D11" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5.0</v>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D12" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.0</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D14" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.0</v>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="7">
-        <v>2.0</v>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D16" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.0</v>
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D17" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.0</v>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D18" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2.0</v>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D19" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="7">
-        <v>2.0</v>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D20" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2.0</v>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D21" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.0</v>
+      <c r="A22" s="6"/>
+      <c r="B22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D22" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.0</v>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D24" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="7">
-        <v>2.0</v>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D25" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="7">
-        <v>2.0</v>
+      <c r="A26" s="6"/>
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D26" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="7">
-        <v>2.0</v>
+      <c r="A28" s="6"/>
+      <c r="B28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D28" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="7">
-        <v>2.0</v>
+      <c r="A30" s="6"/>
+      <c r="B30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D30" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="7">
-        <v>2.0</v>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D31" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="7">
-        <v>5.0</v>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D32" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="7">
-        <v>5.0</v>
+      <c r="A34" s="6"/>
+      <c r="B34" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D34" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="7">
-        <v>2.0</v>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D36" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="7">
-        <v>2.0</v>
+      <c r="A37" s="6"/>
+      <c r="B37" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D37" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="7">
-        <v>2.0</v>
+      <c r="A38" s="6"/>
+      <c r="B38" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D38" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="5"/>
     </row>
     <row r="40">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="7">
-        <v>5.0</v>
+      <c r="A40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D40" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="5"/>
     </row>
     <row r="42">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="7">
-        <v>2.0</v>
+      <c r="A42" s="6"/>
+      <c r="B42" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D42" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="7">
-        <v>2.0</v>
+      <c r="A43" s="6"/>
+      <c r="B43" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D43" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="7">
-        <v>2.0</v>
+      <c r="A44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D44" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="7">
-        <v>2.0</v>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D45" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="7">
-        <v>2.0</v>
+      <c r="A46" s="6"/>
+      <c r="B46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D46" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="7">
-        <v>5.0</v>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D47" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2.0</v>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D48" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="7">
-        <v>5.0</v>
+      <c r="A49" s="6"/>
+      <c r="B49" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D49" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="7">
-        <v>2.0</v>
+      <c r="A50" s="6"/>
+      <c r="B50" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D50" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="7">
-        <v>5.0</v>
+      <c r="A51" s="6"/>
+      <c r="B51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D51" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="7">
-        <v>5.0</v>
+      <c r="A52" s="6"/>
+      <c r="B52" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D52" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="4"/>
+      <c r="A53" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="5"/>
     </row>
     <row r="54">
-      <c r="A54" s="10"/>
-      <c r="B54" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2.0</v>
+      <c r="A54" s="13"/>
+      <c r="B54" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D54" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10"/>
-      <c r="B55" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="7">
-        <v>2.0</v>
+      <c r="A55" s="13"/>
+      <c r="B55" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D55" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10"/>
-      <c r="B56" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56" s="7">
-        <v>5.0</v>
+      <c r="A56" s="13"/>
+      <c r="B56" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D56" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="4"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="5"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="4"/>
+      <c r="A58" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="10"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="10"/>
-      <c r="B59" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="7">
+      <c r="A59" s="13"/>
+      <c r="B59" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="8">
         <v>10.0</v>
       </c>
+      <c r="D59" s="11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="13"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="14"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="12">
+      <c r="B61" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="15">
         <v>10.0</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="8"/>
-      <c r="C62" s="11">
+      <c r="B62" s="10"/>
+      <c r="C62" s="14">
         <f>SUM(C2:C61)</f>
         <v>142</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>54</v>
+      <c r="D62" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="8"/>
-      <c r="C63" s="11"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="14"/>
     </row>
     <row r="64">
-      <c r="C64" s="11"/>
+      <c r="C64" s="14"/>
     </row>
     <row r="65">
-      <c r="C65" s="11"/>
+      <c r="C65" s="14"/>
     </row>
     <row r="66">
-      <c r="C66" s="11"/>
+      <c r="C66" s="14"/>
     </row>
     <row r="67">
-      <c r="C67" s="11"/>
+      <c r="C67" s="14"/>
     </row>
     <row r="68">
-      <c r="C68" s="11"/>
+      <c r="C68" s="14"/>
     </row>
     <row r="69">
-      <c r="C69" s="11"/>
+      <c r="C69" s="14"/>
     </row>
     <row r="70">
-      <c r="C70" s="11"/>
+      <c r="C70" s="14"/>
     </row>
     <row r="71">
-      <c r="C71" s="11"/>
+      <c r="C71" s="14"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1217,534 +1362,669 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="7">
-        <v>5.0</v>
+      <c r="A3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D3" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="7">
-        <v>5.0</v>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D4" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="6"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="7">
-        <v>2.0</v>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2.0</v>
+      <c r="A8" s="6"/>
+      <c r="B8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D8" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.0</v>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D9" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2.0</v>
+      <c r="A10" s="6"/>
+      <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5.0</v>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D11" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="7">
-        <v>5.0</v>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D12" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.0</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D14" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.0</v>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="7">
-        <v>2.0</v>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D16" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.0</v>
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D17" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.0</v>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D18" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2.0</v>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D19" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="7">
-        <v>2.0</v>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D20" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2.0</v>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D21" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.0</v>
+      <c r="A22" s="6"/>
+      <c r="B22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D22" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.0</v>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D24" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="7">
-        <v>2.0</v>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D25" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="7">
-        <v>2.0</v>
+      <c r="A26" s="6"/>
+      <c r="B26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D26" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="7">
-        <v>2.0</v>
+      <c r="A28" s="6"/>
+      <c r="B28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D28" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="7">
-        <v>2.0</v>
+      <c r="A30" s="6"/>
+      <c r="B30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D30" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="7">
-        <v>2.0</v>
+      <c r="A31" s="6"/>
+      <c r="B31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D31" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="7">
-        <v>5.0</v>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D32" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="7">
-        <v>5.0</v>
+      <c r="A34" s="6"/>
+      <c r="B34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D34" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="7">
-        <v>2.0</v>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D36" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="7">
-        <v>2.0</v>
+      <c r="A37" s="6"/>
+      <c r="B37" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D37" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="7">
-        <v>2.0</v>
+      <c r="A38" s="6"/>
+      <c r="B38" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D38" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="5"/>
     </row>
     <row r="40">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="7">
-        <v>5.0</v>
+      <c r="A40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D40" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="5"/>
     </row>
     <row r="42">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="7">
-        <v>2.0</v>
+      <c r="A42" s="6"/>
+      <c r="B42" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D42" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="7">
-        <v>2.0</v>
+      <c r="A43" s="6"/>
+      <c r="B43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D43" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="7">
-        <v>2.0</v>
+      <c r="A44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D44" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="7">
-        <v>2.0</v>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D45" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="7">
-        <v>2.0</v>
+      <c r="A46" s="6"/>
+      <c r="B46" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D46" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="7">
-        <v>5.0</v>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D47" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2.0</v>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D48" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="7">
-        <v>5.0</v>
+      <c r="A49" s="6"/>
+      <c r="B49" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D49" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="7">
-        <v>2.0</v>
+      <c r="A50" s="6"/>
+      <c r="B50" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D50" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="7">
-        <v>5.0</v>
+      <c r="A51" s="6"/>
+      <c r="B51" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D51" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="7">
-        <v>5.0</v>
+      <c r="A52" s="6"/>
+      <c r="B52" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D52" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="4"/>
+      <c r="A53" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="5"/>
     </row>
     <row r="54">
-      <c r="A54" s="10"/>
-      <c r="B54" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2.0</v>
+      <c r="A54" s="13"/>
+      <c r="B54" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D54" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10"/>
-      <c r="B55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="7">
-        <v>2.0</v>
+      <c r="A55" s="13"/>
+      <c r="B55" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D55" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10"/>
-      <c r="B56" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="7">
-        <v>5.0</v>
+      <c r="A56" s="13"/>
+      <c r="B56" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="D56" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="4"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="5"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="4"/>
+      <c r="A58" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="10"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59">
-      <c r="A59" s="10"/>
-      <c r="B59" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C59" s="7">
+      <c r="A59" s="13"/>
+      <c r="B59" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="8">
         <v>10.0</v>
       </c>
+      <c r="D59" s="11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="10"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="13"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="14"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" s="12">
+      <c r="A61" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="15">
         <v>10.0</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="8"/>
-      <c r="C62" s="11">
+      <c r="B62" s="10"/>
+      <c r="C62" s="14">
         <f>SUM(C2:C61)</f>
         <v>142</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>54</v>
+      <c r="D62" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="8"/>
-      <c r="C63" s="11"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="14"/>
     </row>
     <row r="64">
-      <c r="C64" s="11"/>
+      <c r="C64" s="14"/>
     </row>
     <row r="65">
-      <c r="C65" s="11"/>
+      <c r="C65" s="14"/>
     </row>
     <row r="66">
-      <c r="C66" s="11"/>
+      <c r="C66" s="14"/>
     </row>
     <row r="67">
-      <c r="C67" s="11"/>
+      <c r="C67" s="14"/>
     </row>
     <row r="68">
-      <c r="C68" s="11"/>
+      <c r="C68" s="14"/>
     </row>
     <row r="69">
-      <c r="C69" s="11"/>
+      <c r="C69" s="14"/>
     </row>
     <row r="70">
-      <c r="C70" s="11"/>
+      <c r="C70" s="14"/>
     </row>
     <row r="71">
-      <c r="C71" s="11"/>
+      <c r="C71" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Correction CSGames.xlsx
+++ b/Correction CSGames.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
   <si>
     <t>Page</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>Créer un code de qualité : design patterns, tests, structure de code, code smell, etc.</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>Qualité de l'expérience utilisateur et de l'interface graphique</t>
   </si>
   <si>
     <t>Total</t>
@@ -334,6 +340,9 @@
   </si>
   <si>
     <t>Write high-quality code: design patterns, tests, code structure, avoiding code smells, etc.</t>
+  </si>
+  <si>
+    <t>Overall quality of the UI/UX</t>
   </si>
 </sst>
 </file>
@@ -1295,22 +1304,29 @@
         <v>54</v>
       </c>
       <c r="C61" s="15">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="15">
         <v>10.0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="10"/>
-      <c r="C62" s="14">
-        <f>SUM(C2:C61)</f>
-        <v>142</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="10"/>
-      <c r="C63" s="14"/>
+      <c r="C63" s="14">
+        <f>SUM(C2:C62)</f>
+        <v>147</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="64">
       <c r="C64" s="14"/>
@@ -1363,19 +1379,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" s="8">
         <v>5.0</v>
@@ -1387,7 +1403,7 @@
     <row r="4">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8">
         <v>5.0</v>
@@ -1410,7 +1426,7 @@
     <row r="7">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="8">
         <v>2.0</v>
@@ -1422,7 +1438,7 @@
     <row r="8">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" s="8">
         <v>2.0</v>
@@ -1434,7 +1450,7 @@
     <row r="9">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="8">
         <v>2.0</v>
@@ -1446,7 +1462,7 @@
     <row r="10">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="8">
         <v>2.0</v>
@@ -1458,7 +1474,7 @@
     <row r="11">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" s="8">
         <v>5.0</v>
@@ -1470,7 +1486,7 @@
     <row r="12">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" s="8">
         <v>5.0</v>
@@ -1487,7 +1503,7 @@
     <row r="14">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" s="8">
         <v>2.0</v>
@@ -1499,7 +1515,7 @@
     <row r="15">
       <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C15" s="8">
         <v>2.0</v>
@@ -1511,7 +1527,7 @@
     <row r="16">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" s="8">
         <v>2.0</v>
@@ -1523,7 +1539,7 @@
     <row r="17">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" s="8">
         <v>2.0</v>
@@ -1535,7 +1551,7 @@
     <row r="18">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" s="8">
         <v>2.0</v>
@@ -1547,7 +1563,7 @@
     <row r="19">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C19" s="8">
         <v>2.0</v>
@@ -1559,7 +1575,7 @@
     <row r="20">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="8">
         <v>2.0</v>
@@ -1571,7 +1587,7 @@
     <row r="21">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="8">
         <v>2.0</v>
@@ -1583,7 +1599,7 @@
     <row r="22">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" s="8">
         <v>2.0</v>
@@ -1600,7 +1616,7 @@
     <row r="24">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" s="8">
         <v>2.0</v>
@@ -1612,7 +1628,7 @@
     <row r="25">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" s="8">
         <v>2.0</v>
@@ -1624,7 +1640,7 @@
     <row r="26">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C26" s="8">
         <v>2.0</v>
@@ -1641,7 +1657,7 @@
     <row r="28">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" s="8">
         <v>2.0</v>
@@ -1658,7 +1674,7 @@
     <row r="30">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C30" s="8">
         <v>2.0</v>
@@ -1670,7 +1686,7 @@
     <row r="31">
       <c r="A31" s="6"/>
       <c r="B31" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C31" s="8">
         <v>2.0</v>
@@ -1682,7 +1698,7 @@
     <row r="32">
       <c r="A32" s="6"/>
       <c r="B32" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C32" s="8">
         <v>5.0</v>
@@ -1699,7 +1715,7 @@
     <row r="34">
       <c r="A34" s="6"/>
       <c r="B34" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34" s="8">
         <v>5.0</v>
@@ -1716,7 +1732,7 @@
     <row r="36">
       <c r="A36" s="6"/>
       <c r="B36" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="8">
         <v>2.0</v>
@@ -1728,7 +1744,7 @@
     <row r="37">
       <c r="A37" s="6"/>
       <c r="B37" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C37" s="8">
         <v>2.0</v>
@@ -1740,7 +1756,7 @@
     <row r="38">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38" s="8">
         <v>2.0</v>
@@ -1757,7 +1773,7 @@
     <row r="40">
       <c r="A40" s="6"/>
       <c r="B40" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C40" s="8">
         <v>5.0</v>
@@ -1776,7 +1792,7 @@
     <row r="42">
       <c r="A42" s="6"/>
       <c r="B42" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C42" s="8">
         <v>2.0</v>
@@ -1788,7 +1804,7 @@
     <row r="43">
       <c r="A43" s="6"/>
       <c r="B43" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C43" s="8">
         <v>2.0</v>
@@ -1800,7 +1816,7 @@
     <row r="44">
       <c r="A44" s="6"/>
       <c r="B44" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C44" s="8">
         <v>2.0</v>
@@ -1812,7 +1828,7 @@
     <row r="45">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" s="8">
         <v>2.0</v>
@@ -1824,7 +1840,7 @@
     <row r="46">
       <c r="A46" s="6"/>
       <c r="B46" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C46" s="8">
         <v>2.0</v>
@@ -1836,7 +1852,7 @@
     <row r="47">
       <c r="A47" s="6"/>
       <c r="B47" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C47" s="8">
         <v>5.0</v>
@@ -1848,7 +1864,7 @@
     <row r="48">
       <c r="A48" s="6"/>
       <c r="B48" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C48" s="8">
         <v>2.0</v>
@@ -1860,7 +1876,7 @@
     <row r="49">
       <c r="A49" s="6"/>
       <c r="B49" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C49" s="8">
         <v>5.0</v>
@@ -1872,7 +1888,7 @@
     <row r="50">
       <c r="A50" s="6"/>
       <c r="B50" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C50" s="8">
         <v>2.0</v>
@@ -1884,7 +1900,7 @@
     <row r="51">
       <c r="A51" s="6"/>
       <c r="B51" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C51" s="8">
         <v>5.0</v>
@@ -1896,7 +1912,7 @@
     <row r="52">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C52" s="8">
         <v>5.0</v>
@@ -1915,7 +1931,7 @@
     <row r="54">
       <c r="A54" s="13"/>
       <c r="B54" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C54" s="8">
         <v>2.0</v>
@@ -1927,7 +1943,7 @@
     <row r="55">
       <c r="A55" s="13"/>
       <c r="B55" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C55" s="8">
         <v>2.0</v>
@@ -1939,7 +1955,7 @@
     <row r="56">
       <c r="A56" s="13"/>
       <c r="B56" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C56" s="8">
         <v>5.0</v>
@@ -1963,7 +1979,7 @@
     <row r="59">
       <c r="A59" s="13"/>
       <c r="B59" s="16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C59" s="8">
         <v>10.0</v>
@@ -1979,28 +1995,35 @@
     </row>
     <row r="61">
       <c r="A61" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C61" s="15">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="15">
         <v>10.0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="10"/>
-      <c r="C62" s="14">
-        <f>SUM(C2:C61)</f>
-        <v>142</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="10"/>
-      <c r="C63" s="14"/>
+      <c r="C63" s="14">
+        <f>SUM(C2:C62)</f>
+        <v>147</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="64">
       <c r="C64" s="14"/>
